--- a/artfynd/A 39213-2021 artfynd.xlsx
+++ b/artfynd/A 39213-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 39213-2021 artfynd.xlsx
+++ b/artfynd/A 39213-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,56 +675,47 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>64342912</v>
+        <v>64342988</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ö Röjmyran, Vb</t>
+          <t>SO Röjmyran, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>807026.3158545898</v>
+        <v>806647</v>
       </c>
       <c r="R2" t="n">
-        <v>7172755.985230088</v>
+        <v>7172517</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,28 +745,17 @@
           <t>2012-10-25</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-10-25</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -794,56 +774,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>64343020</v>
+        <v>73777867</v>
       </c>
       <c r="B3" t="n">
-        <v>89338</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>S Röjmyran, Vb</t>
+          <t>Bäckfjärden, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>806899.8893206024</v>
+        <v>806742</v>
       </c>
       <c r="R3" t="n">
-        <v>7172459.07120427</v>
+        <v>7172448</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,22 +839,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2012-10-25</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2012-10-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,34 +853,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>64342963</v>
+        <v>73777868</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,40 +882,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>SO Röjmyran, Vb</t>
+          <t>Bäckfjärden, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>806820.0734359506</v>
+        <v>806501</v>
       </c>
       <c r="R4" t="n">
-        <v>7172506.415954959</v>
+        <v>7172552</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,22 +941,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2012-10-25</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2012-10-25</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,27 +961,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>64342988</v>
+        <v>64343020</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,36 +984,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>SO Röjmyran, Vb</t>
+          <t>S Röjmyran, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>806647.2830212659</v>
+        <v>806900</v>
       </c>
       <c r="R5" t="n">
-        <v>7172517.058935434</v>
+        <v>7172459</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,27 +1047,18 @@
           <t>2012-10-25</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2012-10-25</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1145,15 +1077,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>64342902</v>
+        <v>73777865</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1161,40 +1088,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ö Röjmyran, Vb</t>
+          <t>Bäckfjärden, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>807020.6261869171</v>
+        <v>806959</v>
       </c>
       <c r="R6" t="n">
-        <v>7172807.807022261</v>
+        <v>7172746</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,22 +1142,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2012-10-25</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2012-10-25</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,27 +1162,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>64342975</v>
+        <v>73777864</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1279,40 +1185,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>SO Röjmyran, Vb</t>
+          <t>Bäckfjärden, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>806861.5214538509</v>
+        <v>807009</v>
       </c>
       <c r="R7" t="n">
-        <v>7172486.797347382</v>
+        <v>7172773</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1339,22 +1239,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2012-10-25</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2012-10-25</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1369,27 +1259,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>64343001</v>
+        <v>64343132</v>
       </c>
       <c r="B8" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,21 +1282,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1427,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>806916.3304539941</v>
+        <v>806922</v>
       </c>
       <c r="R8" t="n">
-        <v>7172493.652574277</v>
+        <v>7172441</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,19 +1345,9 @@
           <t>2012-10-25</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2012-10-25</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1500,15 +1375,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>64342918</v>
+        <v>73777866</v>
       </c>
       <c r="B9" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1516,40 +1386,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ö Röjmyran, Vb</t>
+          <t>Bäckfjärden, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>806907.8783383288</v>
+        <v>806878</v>
       </c>
       <c r="R9" t="n">
-        <v>7172628.348403952</v>
+        <v>7172478</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1576,22 +1440,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2012-10-25</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2012-10-25</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,34 +1454,28 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>64343132</v>
+        <v>64343001</v>
       </c>
       <c r="B10" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1635,21 +1483,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1665,10 +1513,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>806922.0617134881</v>
+        <v>806916</v>
       </c>
       <c r="R10" t="n">
-        <v>7172441.396746126</v>
+        <v>7172494</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1698,19 +1546,9 @@
           <t>2012-10-25</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2012-10-25</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1738,15 +1576,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>64342933</v>
+        <v>73777869</v>
       </c>
       <c r="B11" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,40 +1587,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>SO Röjmyran, Vb</t>
+          <t>Bäckfjärden, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>806791.7471552915</v>
+        <v>806918</v>
       </c>
       <c r="R11" t="n">
-        <v>7172644.726131482</v>
+        <v>7172870</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1814,22 +1641,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2012-10-25</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2012-10-25</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1838,34 +1655,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>64343061</v>
+        <v>64342933</v>
       </c>
       <c r="B12" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1873,36 +1684,40 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>S Röjmyran, Vb</t>
+          <t>SO Röjmyran, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>806862.8949253187</v>
+        <v>806792</v>
       </c>
       <c r="R12" t="n">
-        <v>7172451.856522238</v>
+        <v>7172645</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1932,19 +1747,9 @@
           <t>2012-10-25</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2012-10-25</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1975,12 +1780,7 @@
         <v>64343095</v>
       </c>
       <c r="B13" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,10 +1818,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>806814.5113542408</v>
+        <v>806815</v>
       </c>
       <c r="R13" t="n">
-        <v>7172420.101172554</v>
+        <v>7172420</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2051,19 +1851,9 @@
           <t>2012-10-25</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2012-10-25</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2091,56 +1881,51 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>64343113</v>
+        <v>64342902</v>
       </c>
       <c r="B14" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>S Röjmyran, Vb</t>
+          <t>Ö Röjmyran, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>806834.266125851</v>
+        <v>807021</v>
       </c>
       <c r="R14" t="n">
-        <v>7172413.441367395</v>
+        <v>7172808</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2170,28 +1955,17 @@
           <t>2012-10-25</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2012-10-25</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2210,55 +1984,51 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>73777868</v>
+        <v>64342963</v>
       </c>
       <c r="B15" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bäckfjärden, Vb</t>
+          <t>SO Röjmyran, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>806501.0818567255</v>
+        <v>806820</v>
       </c>
       <c r="R15" t="n">
-        <v>7172552.056372417</v>
+        <v>7172506</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2285,22 +2055,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2018-09-04</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-10-25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2018-09-04</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-10-25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2315,31 +2075,26 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Julia Pettersson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Julia Pettersson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>73777867</v>
+        <v>64342975</v>
       </c>
       <c r="B16" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2361,16 +2116,22 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bäckfjärden, Vb</t>
+          <t>SO Röjmyran, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>806741.888124434</v>
+        <v>806862</v>
       </c>
       <c r="R16" t="n">
-        <v>7172447.822418884</v>
+        <v>7172487</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2397,22 +2158,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2018-09-04</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-10-25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2018-09-04</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-10-25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2427,62 +2178,61 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Julia Pettersson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Julia Pettersson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>73777869</v>
+        <v>73777863</v>
       </c>
       <c r="B17" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bäckfjärden, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>806918.049082584</v>
+        <v>806981</v>
       </c>
       <c r="R17" t="n">
-        <v>7172870.155151075</v>
+        <v>7172942</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2512,19 +2262,9 @@
           <t>2018-09-04</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2018-09-04</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2548,342 +2288,6 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>73777864</v>
-      </c>
-      <c r="B18" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>185</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Violettgrå tagellav</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Bryoria nadvornikiana</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Bäckfjärden, Vb</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>807008.9961494595</v>
-      </c>
-      <c r="R18" t="n">
-        <v>7172772.849790085</v>
-      </c>
-      <c r="S18" t="n">
-        <v>10</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Skellefteå</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Bureå</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2018-09-04</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2018-09-04</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Julia Pettersson</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Julia Pettersson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>73777866</v>
-      </c>
-      <c r="B19" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Bäckfjärden, Vb</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>806878.0160457797</v>
-      </c>
-      <c r="R19" t="n">
-        <v>7172478.07524188</v>
-      </c>
-      <c r="S19" t="n">
-        <v>10</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Skellefteå</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Bureå</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2018-09-04</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2018-09-04</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>Julia Pettersson</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>Julia Pettersson</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>73777865</v>
-      </c>
-      <c r="B20" t="n">
-        <v>89338</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>112</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Stjärntagging</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Asterodon ferruginosus</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Pat.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Bäckfjärden, Vb</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>806959.2393419909</v>
-      </c>
-      <c r="R20" t="n">
-        <v>7172746.151325203</v>
-      </c>
-      <c r="S20" t="n">
-        <v>10</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Skellefteå</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Bureå</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2018-09-04</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2018-09-04</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Julia Pettersson</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Julia Pettersson</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39213-2021 artfynd.xlsx
+++ b/artfynd/A 39213-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -776,6 +781,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64342933</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64343095</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64342963</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1086,6 +1106,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64342975</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1185,6 +1210,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64342988</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1282,6 +1312,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73777867</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1384,6 +1419,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73777868</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64343020</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1585,6 +1630,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73777865</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73777864</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1786,6 +1841,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64343132</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1883,6 +1943,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73777866</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1987,6 +2052,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64343001</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2084,6 +2154,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73777869</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2187,6 +2262,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64342902</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2288,8 +2368,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73777863</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>